--- a/Result/profitability/3041.xlsx
+++ b/Result/profitability/3041.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.22</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.65125</v>
+        <v>-0.5462499999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>30.5975</v>
+        <v>34.39625</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.1</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.5075000000000001</v>
+        <v>-0.4825</v>
       </c>
       <c r="N3" t="n">
-        <v>31.93875</v>
+        <v>35.25624999999999</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.49</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.395</v>
+        <v>-0.37125</v>
       </c>
       <c r="N4" t="n">
-        <v>33.31375</v>
+        <v>35.015</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.04</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.35</v>
+        <v>-0.2887500000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>31.44</v>
+        <v>35.87375</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.54</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.195</v>
+        <v>-0.09250000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>35.76875</v>
+        <v>38.17625</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1152,13 +1152,13 @@
         <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.7</v>
       </c>
       <c r="M7" t="n">
-        <v>0.02124999999999999</v>
+        <v>0.165</v>
       </c>
       <c r="N7" t="n">
-        <v>37.9975</v>
+        <v>43.61125</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>1.28</v>
       </c>
       <c r="M8" t="n">
-        <v>0.35125</v>
+        <v>0.385</v>
       </c>
       <c r="N8" t="n">
-        <v>43.07625</v>
+        <v>43.88375</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1648,7 +1648,7 @@
         <v>0.61375</v>
       </c>
       <c r="N10" t="n">
-        <v>42.26374999999999</v>
+        <v>42.26375</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -1899,7 +1899,7 @@
         <v>0.57</v>
       </c>
       <c r="M12" t="n">
-        <v>0.73</v>
+        <v>0.7300000000000001</v>
       </c>
       <c r="N12" t="n">
         <v>44.55625</v>
@@ -2026,7 +2026,7 @@
         <v>0.55</v>
       </c>
       <c r="M13" t="n">
-        <v>0.80375</v>
+        <v>0.8037500000000001</v>
       </c>
       <c r="N13" t="n">
         <v>48.4025</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3041</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>478</v>
+      </c>
+      <c r="D75" t="n">
+        <v>221</v>
+      </c>
+      <c r="E75" t="n">
+        <v>257</v>
+      </c>
+      <c r="F75" t="n">
+        <v>53.84</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-19</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-3.93%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-9</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-28</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-29</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.7050000000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>31.76</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.5625</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>6.460000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1363444491346559</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>35.47</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>1.930865541643985</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
